--- a/Дело3а-78-2026Таганай/02_Отчёты/00_Ведомость_02_Отчёты_экспертные.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/00_Ведомость_02_Отчёты_экспертные.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость 02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 02'!$B$11:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 02'!$B$11:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ведомость 02'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -128,8 +128,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4EC"/>
-        <bgColor rgb="00E8F4EC"/>
+        <fgColor rgb="00FFF6CC"/>
+        <bgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,9 +195,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -568,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -616,7 +613,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -637,7 +634,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.92957187089</v>
+        <v>46158.29715978116</v>
       </c>
     </row>
     <row r="9">
@@ -795,85 +792,54 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>02.4</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Сводная ведомость</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Сводная_ведомость.xlsx</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>46157.92520788052</v>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>7 КБ</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Подсказки:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Подсказки:</t>
+          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>• Перезапуск скрипта перезапишет файл (в т.ч. наименования).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B11:H15"/>
+  <autoFilter ref="B11:H14"/>
   <mergeCells count="10">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="E9:H9"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B17:H17"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Дело3а-78-2026Таганай/02_Отчёты/00_Ведомость_02_Отчёты_экспертные.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/00_Ведомость_02_Отчёты_экспертные.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46158.29715978116</v>
+        <v>46158.37371883278</v>
       </c>
     </row>
     <row r="9">
